--- a/reports/売上目標_再設定_2026-09.xlsx
+++ b/reports/売上目標_再設定_2026-09.xlsx
@@ -844,7 +844,7 @@
         <v>1.1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1230119</v>
+        <v>1205772</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1271123</v>
+        <v>1245965</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1494135</v>
+        <v>1466542</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>100000</v>
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1148111</v>
+        <v>1125387</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0.75</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1562127</v>
+        <v>1536157</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>250000</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>993091</v>
+        <v>974425</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>50000</v>
@@ -994,7 +994,7 @@
         <v>0.9</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>902089</v>
+        <v>884234</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>

--- a/reports/売上目標_再設定_2026-09.xlsx
+++ b/reports/売上目標_再設定_2026-09.xlsx
@@ -844,7 +844,7 @@
         <v>1.1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1205772</v>
+        <v>1042136</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1245965</v>
+        <v>1076874</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1466542</v>
+        <v>1281087</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>100000</v>
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1125387</v>
+        <v>972660</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0.75</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1536157</v>
+        <v>1361612</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>250000</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>974425</v>
+        <v>848971</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>50000</v>
@@ -994,7 +994,7 @@
         <v>0.9</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>884234</v>
+        <v>764233</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>

--- a/reports/売上目標_再設定_2026-09.xlsx
+++ b/reports/売上目標_再設定_2026-09.xlsx
@@ -844,7 +844,7 @@
         <v>1.1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1042136</v>
+        <v>1044349</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1076874</v>
+        <v>1079161</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1281087</v>
+        <v>1283596</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>100000</v>
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>972660</v>
+        <v>974726</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0.75</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1361612</v>
+        <v>1363973</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>250000</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>848971</v>
+        <v>850668</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>50000</v>
@@ -994,7 +994,7 @@
         <v>0.9</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>764233</v>
+        <v>765856</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>

--- a/reports/売上目標_再設定_2026-09.xlsx
+++ b/reports/売上目標_再設定_2026-09.xlsx
@@ -814,7 +814,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>750000</v>
+        <v>740909</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>100000</v>
@@ -844,7 +844,7 @@
         <v>1.1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1044349</v>
+        <v>1045713</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1079161</v>
+        <v>1080570</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1283596</v>
+        <v>1285141</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>100000</v>
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>974726</v>
+        <v>975999</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0.75</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1363973</v>
+        <v>1365427</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>250000</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>850668</v>
+        <v>851713</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>50000</v>
@@ -994,7 +994,7 @@
         <v>0.9</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>765856</v>
+        <v>766856</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>

--- a/reports/売上目標_再設定_2026-09.xlsx
+++ b/reports/売上目標_再設定_2026-09.xlsx
@@ -814,10 +814,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>740909</v>
+        <v>698422</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>100000</v>
+        <v>48422</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0.7</v>
@@ -844,7 +844,7 @@
         <v>1.1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1045713</v>
+        <v>1052086</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1080570</v>
+        <v>1087156</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1285141</v>
+        <v>1292364</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>100000</v>
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>975999</v>
+        <v>981947</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0.75</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1365427</v>
+        <v>1372225</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>250000</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>851713</v>
+        <v>856599</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>50000</v>
@@ -994,7 +994,7 @@
         <v>0.9</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>766856</v>
+        <v>771530</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>
